--- a/results/by_outcome/full_results_education_PGI_pgi_cognitive.xlsx
+++ b/results/by_outcome/full_results_education_PGI_pgi_cognitive.xlsx
@@ -6,97 +6,54 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Full results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="For plotting" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="For plotting" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">Index</t>
+  </si>
   <si>
     <t xml:space="preserve">Outcome</t>
   </si>
   <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emptyind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emptyfam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totalvar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">condind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">condfam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">completeind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">completefam</t>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGI</t>
   </si>
   <si>
     <t xml:space="preserve">Sibcorr</t>
   </si>
   <si>
-    <t xml:space="preserve">condcorr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
+    <t xml:space="preserve">education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pgi_cognitive</t>
   </si>
   <si>
     <t xml:space="preserve">IOLIB</t>
   </si>
   <si>
     <t xml:space="preserve">IORAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NULL MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONDITIONAL MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPLETE MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pgi_cognitive</t>
   </si>
   <si>
     <t xml:space="preserve">diff</t>
@@ -456,172 +413,25 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.662718487922359</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.337359370384728</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.00007785830709</v>
-      </c>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2" t="n">
-        <v>0.337333106200155</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.321884563569226</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.011614845846822</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.0146311646176825</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.333499409416048</v>
-      </c>
-      <c r="O2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3" t="n">
-        <v>0.659701934306026</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.321909624956423</v>
-      </c>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4" t="n">
-        <v>0.648086184146969</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.26381347412667</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
-      <c r="M4"/>
-      <c r="N4"/>
-      <c r="O4" t="n">
-        <v>0.351964270817838</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>0.337333106200155</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0159208492812001</v>
+        <v>0.0155932926341852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.303554609355834</v>
+        <v>0.305510288822421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.368345809044646</v>
+        <v>0.366955550291458</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -630,27 +440,27 @@
         <v>4334</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.333499409416048</v>
+        <v>0.336001138176404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0159090544667195</v>
+        <v>0.0148958890313119</v>
       </c>
       <c r="E3" t="n">
-        <v>0.301436764611009</v>
+        <v>0.307023694568391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.364549386339315</v>
+        <v>0.365404903181197</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -659,27 +469,27 @@
         <v>4334</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>0.351964270817838</v>
+        <v>0.354465999578194</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0161172841969513</v>
+        <v>0.0150076759203985</v>
       </c>
       <c r="E4" t="n">
-        <v>0.318425794710161</v>
+        <v>0.325320580667586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.382637811878157</v>
+        <v>0.385036818134709</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -688,36 +498,36 @@
         <v>4334</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01846486140179</v>
+        <v>0.0184648614017899</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00322469541874006</v>
+        <v>0.00336158413205294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0126847383071238</v>
+        <v>0.0120354519450796</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0255389967680165</v>
+        <v>0.0251566028095088</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00000000513891229569907</v>
+        <v>0.0000000197688044822897</v>
       </c>
       <c r="H5" t="n">
         <v>4334</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
